--- a/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
+++ b/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
@@ -509,10 +509,10 @@
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10.05" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="19.25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>

--- a/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
+++ b/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,11 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00A6A6A6"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -86,13 +91,45 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -115,32 +152,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,394 +560,406 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MINUTA DE REUNIÓN</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>INSERTE SU LOGO
+(clic derecho &gt; Insertar imagen)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="4" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Hora inicio/fin</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Lugar</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Elaboró</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>ASISTENTES</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Puesto / Área</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Firma</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr"/>
+      <c r="E8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>ORDEN DEL DÍA</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>DESARROLLO / ACUERDOS</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>COMPROMISOS</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Actividad</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Fecha límite</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Estatus</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="4" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="4" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="4" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="9" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="4" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n">
+      <c r="A38" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="4" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="4" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="n">
+      <c r="A40" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="4" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="4" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="9" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="4" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="n">
+      <c r="A43" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="4" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n"/>
-      <c r="C47" s="9" t="n"/>
+      <c r="A47" s="14" t="n"/>
+      <c r="C47" s="14" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Elaboró</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>Revisó</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A47"/>
     <mergeCell ref="C48"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A48"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D1:E2"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A25:E30"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="C47"/>
     <mergeCell ref="A19:E22"/>
     <mergeCell ref="B4:C4"/>
@@ -926,7 +982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -934,61 +990,71 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Minuta de reunión</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Guía de uso</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Llena los datos generales y registra a los asistentes.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Anota el orden del día y los acuerdos tomados.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>En la tabla de compromisos define responsable, fecha límite y estatus (lista desplegable).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Distribuye la minuta a los asistentes dentro de las 24 horas siguientes a la reunión.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas amarillas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
         </is>

--- a/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
+++ b/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,35 +32,77 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
-    </font>
-    <font>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00595959"/>
-    </font>
-    <font>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-    </font>
-    <font>
+      <color rgb="001B6B73"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <i val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="002B2B2B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="008A97A3"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -72,31 +114,45 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="000B2A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00E6ECF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E5"/>
+        <fgColor rgb="00FFFCF0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -133,58 +189,78 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </bottom>
     </border>
     <border>
       <bottom style="thin"/>
     </border>
+    <border>
+      <top style="thick">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -547,6 +623,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Minuta de reunión</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Formato administrativo editable · México</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>CÓMO USARLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="B11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Llena los datos generales y registra a los asistentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="B12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Anota el orden del día y los acuerdos tomados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="B13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>En la tabla de compromisos define responsable, fecha límite y estatus (lista desplegable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="B14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Distribuye la minuta a los asistentes dentro de las 24 horas siguientes a la reunión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>LEYENDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Celda de captura: escribe aquí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Cálculo automático: no la modifiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="12" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Encabezados y títulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B2A4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -560,52 +820,54 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>MINUTA DE REUNIÓN</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="7" t="n"/>
+      <c r="E1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="18" t="inlineStr"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="21" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="9" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n"/>
+      <c r="E3" s="23" t="n"/>
       <c r="F3" s="9" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="9" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>Hora inicio/fin</t>
         </is>
@@ -614,14 +876,14 @@
       <c r="F4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Lugar</t>
         </is>
       </c>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Elaboró</t>
         </is>
@@ -630,37 +892,37 @@
       <c r="F5" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>ASISTENTES</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Puesto / Área</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Firma</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr"/>
+      <c r="E8" s="25" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B9" s="9" t="n"/>
@@ -668,7 +930,7 @@
       <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B10" s="9" t="n"/>
@@ -676,7 +938,7 @@
       <c r="D10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B11" s="9" t="n"/>
@@ -684,7 +946,7 @@
       <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -692,7 +954,7 @@
       <c r="D12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n">
+      <c r="A13" s="11" t="n">
         <v>5</v>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -700,7 +962,7 @@
       <c r="D13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n">
+      <c r="A14" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B14" s="9" t="n"/>
@@ -708,7 +970,7 @@
       <c r="D14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n">
+      <c r="A15" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B15" s="9" t="n"/>
@@ -716,7 +978,7 @@
       <c r="D15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="n">
+      <c r="A16" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="9" t="n"/>
@@ -724,7 +986,7 @@
       <c r="D16" s="9" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>ORDEN DEL DÍA</t>
         </is>
@@ -759,7 +1021,7 @@
       <c r="E22" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>DESARROLLO / ACUERDOS</t>
         </is>
@@ -808,140 +1070,140 @@
       <c r="E30" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>COMPROMISOS</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>Actividad</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>Fecha límite</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>Estatus</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="n">
+      <c r="A34" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B34" s="9" t="n"/>
       <c r="C34" s="9" t="n"/>
-      <c r="D34" s="10" t="n"/>
+      <c r="D34" s="23" t="n"/>
       <c r="E34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="n">
+      <c r="A35" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="9" t="n"/>
-      <c r="D35" s="10" t="n"/>
+      <c r="D35" s="23" t="n"/>
       <c r="E35" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="n">
+      <c r="A36" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="9" t="n"/>
-      <c r="D36" s="10" t="n"/>
+      <c r="D36" s="23" t="n"/>
       <c r="E36" s="9" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="n">
+      <c r="A37" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="n"/>
-      <c r="D37" s="10" t="n"/>
+      <c r="D37" s="23" t="n"/>
       <c r="E37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="n">
+      <c r="A38" s="11" t="n">
         <v>5</v>
       </c>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="9" t="n"/>
-      <c r="D38" s="10" t="n"/>
+      <c r="D38" s="23" t="n"/>
       <c r="E38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="n">
+      <c r="A39" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="9" t="n"/>
-      <c r="D39" s="10" t="n"/>
+      <c r="D39" s="23" t="n"/>
       <c r="E39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="n">
+      <c r="A40" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B40" s="9" t="n"/>
       <c r="C40" s="9" t="n"/>
-      <c r="D40" s="10" t="n"/>
+      <c r="D40" s="23" t="n"/>
       <c r="E40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="n">
+      <c r="A41" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="9" t="n"/>
-      <c r="D41" s="10" t="n"/>
+      <c r="D41" s="23" t="n"/>
       <c r="E41" s="9" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="n">
+      <c r="A42" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="9" t="n"/>
-      <c r="D42" s="10" t="n"/>
+      <c r="D42" s="23" t="n"/>
       <c r="E42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="n">
+      <c r="A43" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="n"/>
-      <c r="D43" s="10" t="n"/>
+      <c r="D43" s="23" t="n"/>
       <c r="E43" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="n"/>
-      <c r="C47" s="14" t="n"/>
+      <c r="A47" s="26" t="n"/>
+      <c r="C47" s="26" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>Elaboró</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>Revisó</t>
         </is>
@@ -972,95 +1234,14 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="16" t="inlineStr">
-        <is>
-          <t>Minuta de reunión</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Guía de uso</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Llena los datos generales y registra a los asistentes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Anota el orden del día y los acuerdos tomados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>En la tabla de compromisos define responsable, fecha límite y estatus (lista desplegable).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Distribuye la minuta a los asistentes dentro de las 24 horas siguientes a la reunión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas amarillas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Página &amp;P&amp;R&amp;8 Impreso: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
+++ b/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -232,7 +232,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -252,10 +254,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -696,6 +703,7 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -753,6 +761,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -784,6 +793,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="13" t="n"/>
@@ -798,6 +808,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -891,6 +902,7 @@
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
@@ -922,7 +934,7 @@
       <c r="E8" s="25" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="26" t="n">
         <v>1</v>
       </c>
       <c r="B9" s="9" t="n"/>
@@ -930,7 +942,7 @@
       <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="26" t="n">
         <v>2</v>
       </c>
       <c r="B10" s="9" t="n"/>
@@ -938,7 +950,7 @@
       <c r="D10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="26" t="n">
         <v>3</v>
       </c>
       <c r="B11" s="9" t="n"/>
@@ -946,7 +958,7 @@
       <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="26" t="n">
         <v>4</v>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -954,7 +966,7 @@
       <c r="D12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="26" t="n">
         <v>5</v>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -962,7 +974,7 @@
       <c r="D13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="26" t="n">
         <v>6</v>
       </c>
       <c r="B14" s="9" t="n"/>
@@ -970,7 +982,7 @@
       <c r="D14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="26" t="n">
         <v>7</v>
       </c>
       <c r="B15" s="9" t="n"/>
@@ -978,13 +990,14 @@
       <c r="D15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="26" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="9" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
@@ -1020,6 +1033,7 @@
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
         <is>
@@ -1069,6 +1083,7 @@
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
@@ -1104,7 +1119,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="26" t="n">
         <v>1</v>
       </c>
       <c r="B34" s="9" t="n"/>
@@ -1113,7 +1128,7 @@
       <c r="E34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="26" t="n">
         <v>2</v>
       </c>
       <c r="B35" s="9" t="n"/>
@@ -1122,7 +1137,7 @@
       <c r="E35" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="26" t="n">
         <v>3</v>
       </c>
       <c r="B36" s="9" t="n"/>
@@ -1131,7 +1146,7 @@
       <c r="E36" s="9" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="26" t="n">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="n"/>
@@ -1140,7 +1155,7 @@
       <c r="E37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n">
+      <c r="A38" s="26" t="n">
         <v>5</v>
       </c>
       <c r="B38" s="9" t="n"/>
@@ -1149,7 +1164,7 @@
       <c r="E38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n">
+      <c r="A39" s="26" t="n">
         <v>6</v>
       </c>
       <c r="B39" s="9" t="n"/>
@@ -1158,7 +1173,7 @@
       <c r="E39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="26" t="n">
         <v>7</v>
       </c>
       <c r="B40" s="9" t="n"/>
@@ -1167,7 +1182,7 @@
       <c r="E40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n">
+      <c r="A41" s="26" t="n">
         <v>8</v>
       </c>
       <c r="B41" s="9" t="n"/>
@@ -1176,7 +1191,7 @@
       <c r="E41" s="9" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n">
+      <c r="A42" s="26" t="n">
         <v>9</v>
       </c>
       <c r="B42" s="9" t="n"/>
@@ -1185,7 +1200,7 @@
       <c r="E42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="26" t="n">
         <v>10</v>
       </c>
       <c r="B43" s="9" t="n"/>
@@ -1193,23 +1208,27 @@
       <c r="D43" s="23" t="n"/>
       <c r="E43" s="9" t="n"/>
     </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
-      <c r="A47" s="26" t="n"/>
-      <c r="C47" s="26" t="n"/>
+      <c r="A47" s="27" t="n"/>
+      <c r="C47" s="27" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="inlineStr">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>Elaboró</t>
         </is>
       </c>
-      <c r="C48" s="27" t="inlineStr">
+      <c r="C48" s="28" t="inlineStr">
         <is>
           <t>Revisó</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="15">
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A47"/>

--- a/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
+++ b/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTADA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMATO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,80 +30,133 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="001B6B73"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="30"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <i val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="26"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00C9D3DB"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="001B6B73"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="000B2A4A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C9A227"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="002B2B2B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="005B6B78"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="008A97A3"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -133,7 +187,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -205,69 +259,123 @@
       <bottom style="thin"/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thick">
         <color rgb="00C9A227"/>
       </top>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="00C9A227"/>
-      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,22 +742,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -658,157 +772,491 @@
       </c>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>VERSIÓN 2.0  ·  MÉXICO</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Minuta de reunión</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>MINUTA DE REUNIÓN</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Formato administrativo editable · México</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Formato administrativo profesional · editable · listo para imprimir</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="n"/>
       <c r="D7" s="1" t="n"/>
-    </row>
-    <row r="8" ht="6" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>FÓRMULAS AUTOMÁTICAS</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>LISTAS DESPLEGABLES</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>HOJAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>LISTO PARA IMPRIMIR</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n"/>
+    </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>¿QUÉ INCLUYE ESTE ARCHIVO?</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>FORMATO</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Hoja principal de captura. Aquí registras tu información; las celdas grises calculan solas.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>AYUDA</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Preguntas frecuentes, glosario y lista de verificación para cerrar tu periodo.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>CÓMO USARLO</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="7" t="n">
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Llena los datos generales y registra a los asistentes.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="B12" s="7" t="n">
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Anota el orden del día y los acuerdos tomados.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="7" t="n">
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>En la tabla de compromisos define responsable, fecha límite y estatus (lista desplegable).</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="7" t="n">
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Distribuye la minuta a los asistentes dentro de las 24 horas siguientes a la reunión.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="7" t="n">
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>LEYENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Celda de captura: escribe aquí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="11" t="inlineStr"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Cálculo automático: no la modifiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Encabezados y títulos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
-        </is>
-      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Envía la minuta dentro de las 24 horas posteriores a la reunión.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Todo compromiso necesita responsable y fecha límite.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Da seguimiento a los pendientes al inicio de la siguiente reunión.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Mantén los acuerdos redactados en forma clara y medible.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="17" t="inlineStr"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="19" t="inlineStr"/>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="15">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="C28:F28"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -832,400 +1280,517 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>MINUTA DE REUNIÓN</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="E1" s="17" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="4" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="18" t="inlineStr"/>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="21" t="n"/>
+      <c r="A2" s="25" t="inlineStr"/>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="27" t="n"/>
+      <c r="E2" s="28" t="n"/>
+      <c r="F2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="22" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="E3" s="23" t="n"/>
-      <c r="F3" s="9" t="n"/>
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>EMPRESA</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E3" s="30" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>Tema</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>Hora inicio/fin</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>TEMA</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>HORA INICIO/FIN</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Lugar</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>Elaboró</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-    </row>
-    <row r="6"/>
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>LUGAR</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>ELABORÓ</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+    </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>ASISTENTES</t>
         </is>
       </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>Puesto / Área</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>Firma</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr"/>
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>NOMBRE</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>PUESTO / ÁREA</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>FIRMA</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr"/>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-    </row>
-    <row r="17"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>ORDEN DEL DÍA</t>
         </is>
       </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-    </row>
-    <row r="23"/>
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+    </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>DESARROLLO / ACUERDOS</t>
         </is>
       </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
+      <c r="A25" s="17" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n"/>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
+      <c r="A27" s="17" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
+      <c r="A28" s="17" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n"/>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
+      <c r="A29" s="17" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-    </row>
-    <row r="31"/>
+      <c r="A30" s="17" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>COMPROMISOS</t>
         </is>
       </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>Actividad</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="D33" s="25" t="inlineStr">
-        <is>
-          <t>Fecha límite</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>Estatus</t>
-        </is>
-      </c>
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>FECHA LÍMITE</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>ESTATUS</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="n">
+      <c r="A34" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="9" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="n">
+      <c r="A35" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="9" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="n">
+      <c r="A36" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="9" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="30" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="n">
+      <c r="A37" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="9" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="n">
+      <c r="A38" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="9" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="30" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="26" t="n">
+      <c r="A39" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="9" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="4" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="n">
+      <c r="A40" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="9" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="30" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="n">
+      <c r="A41" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="9" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="n">
+      <c r="A42" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="9" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="30" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="n">
+      <c r="A43" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="23" t="n"/>
-      <c r="E43" s="9" t="n"/>
-    </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+    </row>
     <row r="47">
-      <c r="A47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
+      <c r="A47" s="34" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="34" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="28" t="inlineStr">
-        <is>
-          <t>Elaboró</t>
-        </is>
-      </c>
-      <c r="C48" s="28" t="inlineStr">
-        <is>
-          <t>Revisó</t>
-        </is>
-      </c>
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>ELABORÓ</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="35" t="inlineStr">
+        <is>
+          <t>REVISÓ</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -1263,4 +1828,349 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B6B73"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="36" t="inlineStr">
+        <is>
+          <t>AYUDA Y PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>MINUTA DE REUNIÓN</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>¿Cuánto debe durar una minuta?</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>Una o dos páginas; registra decisiones, no cada comentario.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>¿Debe firmarse?</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="inlineStr">
+        <is>
+          <t>Es recomendable en reuniones de comité, juntas con clientes o asuntos legales.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>¿Por qué no puedo escribir en algunas celdas?</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="inlineStr">
+        <is>
+          <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>¿Cómo agrego mi logotipo?</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>¿Con qué versiones de Excel funciona?</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>¿Por qué la letra se ve diferente?</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>¿Puedo usarlo en varias empresas o por varios años?</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="inlineStr">
+        <is>
+          <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>GLOSARIO</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>ORDEN DEL DÍA</t>
+        </is>
+      </c>
+      <c r="D16" s="41" t="inlineStr">
+        <is>
+          <t>Temas a tratar.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>ACUERDO</t>
+        </is>
+      </c>
+      <c r="D17" s="41" t="inlineStr">
+        <is>
+          <t>Decisión tomada en la reunión.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>COMPROMISO</t>
+        </is>
+      </c>
+      <c r="D18" s="41" t="inlineStr">
+        <is>
+          <t>Actividad asignada con responsable y fecha.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>LISTA DE VERIFICACIÓN (marca ☑ al completar)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>Asistentes registrados</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>Acuerdos redactados</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>Compromisos con responsable y fecha</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>Minuta enviada a todos</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"☐,☑"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
+++ b/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
@@ -50,7 +50,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -94,7 +94,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -117,7 +117,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -145,7 +145,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -1833,7 +1833,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
+++ b/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
@@ -767,7 +767,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1228,7 +1228,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="C37" s="4" t="n"/>

--- a/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
+++ b/plantillas/4_Documentos_y_Actas/03_Minuta_de_Reunion.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMATO" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMATO'!$8:$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,136 +32,143 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="30"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E7C8B"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
-      <color rgb="002B2B2B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -182,12 +191,27 @@
       </patternFill>
     </fill>
     <fill>
+      <gradientFill type="linear" degree="90">
+        <stop position="0">
+          <color rgb="0017426B"/>
+        </stop>
+        <stop position="1">
+          <color rgb="000B2A4A"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -256,6 +280,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
       <bottom style="thin"/>
     </border>
     <border>
@@ -279,6 +317,11 @@
     </border>
     <border>
       <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
         <color rgb="00C9D3DB"/>
       </bottom>
     </border>
@@ -286,24 +329,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -314,19 +357,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -335,43 +386,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -742,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -980,7 +1039,7 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>CÓMO USARLO</t>
+          <t>FICHA TÉCNICA</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -991,77 +1050,87 @@
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="4" t="n"/>
-      <c r="B20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Llena los datos generales y registra a los asistentes.</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Capacidad</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>16 asistentes · 10 compromisos</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Anota el orden del día y los acuerdos tomados.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Compatibilidad</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac)</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>En la tabla de compromisos define responsable, fecha límite y estatus (lista desplegable).</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Idioma y moneda</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Español (México) · Pesos mexicanos (MXN) · IVA 16%</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Distribuye la minuta a los asistentes dentro de las 24 horas siguientes a la reunión.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Protección</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Hojas protegidas sin contraseña (Revisar &gt; Desproteger hoja)</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
       <c r="G23" s="4" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="21" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Arial (disponible en Windows, Mac y Google Sheets)</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
     <row r="25">
@@ -1077,7 +1146,7 @@
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>RECOMENDACIONES DE USO</t>
+          <t>CÓMO USARLO</t>
         </is>
       </c>
       <c r="C26" s="10" t="n"/>
@@ -1088,14 +1157,12 @@
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B27" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Envía la minuta dentro de las 24 horas posteriores a la reunión.</t>
+          <t>Llena los datos generales y registra a los asistentes.</t>
         </is>
       </c>
       <c r="D27" s="4" t="n"/>
@@ -1105,14 +1172,12 @@
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B28" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Todo compromiso necesita responsable y fecha límite.</t>
+          <t>Anota el orden del día y los acuerdos tomados.</t>
         </is>
       </c>
       <c r="D28" s="4" t="n"/>
@@ -1122,14 +1187,12 @@
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B29" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Da seguimiento a los pendientes al inicio de la siguiente reunión.</t>
+          <t>En la tabla de compromisos define responsable, fecha límite y estatus (lista desplegable).</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
@@ -1139,14 +1202,12 @@
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B30" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Mantén los acuerdos redactados en forma clara y medible.</t>
+          <t>Distribuye la minuta a los asistentes dentro de las 24 horas siguientes a la reunión.</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -1154,47 +1215,53 @@
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="36" customHeight="1">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
+      <c r="B31" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1">
+    <row r="32">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="24" customHeight="1">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="17" t="inlineStr"/>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>CELDA DE CAPTURA: escribe aquí.</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
       <c r="G33" s="4" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="21" customHeight="1">
       <c r="A34" s="4" t="n"/>
-      <c r="B34" s="19" t="inlineStr"/>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Envía la minuta dentro de las 24 horas posteriores a la reunión.</t>
         </is>
       </c>
       <c r="D34" s="4" t="n"/>
@@ -1202,12 +1269,16 @@
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="21" customHeight="1">
       <c r="A35" s="4" t="n"/>
-      <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>ENCABEZADOS Y TÍTULOS.</t>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Todo compromiso necesita responsable y fecha límite.</t>
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
@@ -1215,47 +1286,164 @@
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="21" customHeight="1">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Da seguimiento a los pendientes al inicio de la siguiente reunión.</t>
+        </is>
+      </c>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Mantén los acuerdos redactados en forma clara y medible.</t>
+        </is>
+      </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
-      <c r="G37" s="1" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="22" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="23" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="24" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>* CAMPO OBLIGATORIO: complétalo antes de imprimir o enviar.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="15">
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
+  <mergeCells count="20">
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B4:F5"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId2"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
@@ -1272,7 +1460,7 @@
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.05" customWidth="1" min="1" max="1"/>
+    <col width="12.35" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="19.25" customWidth="1" min="4" max="4"/>
@@ -1280,77 +1468,77 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>MINUTA DE REUNIÓN</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="E1" s="24" t="n"/>
+      <c r="E1" s="28" t="n"/>
       <c r="F1" s="4" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr"/>
-      <c r="B2" s="26" t="n"/>
-      <c r="C2" s="26" t="n"/>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="28" t="n"/>
+      <c r="A2" s="29" t="inlineStr"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="32" t="n"/>
       <c r="F2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
-        <is>
-          <t>EMPRESA</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="29" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="17" t="n"/>
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>EMPRESA *</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>FECHA *</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="n"/>
+      <c r="F3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>TEMA</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>HORA INICIO/FIN</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>LUGAR</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>ELABORÓ</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n"/>
@@ -1361,7 +1549,7 @@
       <c r="F6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>ASISTENTES</t>
         </is>
@@ -1372,107 +1560,107 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>NOMBRE</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>PUESTO / ÁREA</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>FIRMA</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr"/>
+      <c r="E8" s="36" t="inlineStr"/>
       <c r="F8" s="4" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="33" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
+      <c r="B9" s="38" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="38" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="33" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="33" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="33" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
+      <c r="B12" s="38" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="38" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="33" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
+      <c r="B13" s="38" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="38" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="33" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="33" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
+      <c r="B15" s="38" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="38" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="33" t="n">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
+      <c r="B16" s="38" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="38" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
     </row>
@@ -1485,7 +1673,7 @@
       <c r="F17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>ORDEN DEL DÍA</t>
         </is>
@@ -1497,35 +1685,35 @@
       <c r="F18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="A19" s="20" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
       <c r="F19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="A21" s="20" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
       <c r="F21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="A22" s="20" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
       <c r="F22" s="4" t="n"/>
     </row>
     <row r="23">
@@ -1537,7 +1725,7 @@
       <c r="F23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>DESARROLLO / ACUERDOS</t>
         </is>
@@ -1549,51 +1737,51 @@
       <c r="F24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="A25" s="20" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
       <c r="F25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="n"/>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="A26" s="20" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
       <c r="F26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
+      <c r="A27" s="20" t="n"/>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
       <c r="F27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="n"/>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
+      <c r="A28" s="20" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
       <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
+      <c r="A29" s="20" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
       <c r="F29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="n"/>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
+      <c r="A30" s="20" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
       <c r="F30" s="4" t="n"/>
     </row>
     <row r="31">
@@ -1605,7 +1793,7 @@
       <c r="F31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>COMPROMISOS</t>
         </is>
@@ -1616,132 +1804,132 @@
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>ACTIVIDAD</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>RESPONSABLE</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D33" s="36" t="inlineStr">
         <is>
           <t>FECHA LÍMITE</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E33" s="36" t="inlineStr">
         <is>
           <t>ESTATUS</t>
         </is>
       </c>
       <c r="F33" s="4" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="33" t="n">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="17" t="n"/>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="17" t="n"/>
+      <c r="B34" s="38" t="n"/>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="38" t="n"/>
       <c r="F34" s="4" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="33" t="n">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="17" t="n"/>
+      <c r="B35" s="38" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="38" t="n"/>
       <c r="F35" s="4" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="33" t="n">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="17" t="n"/>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="17" t="n"/>
+      <c r="B36" s="38" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="38" t="n"/>
       <c r="F36" s="4" t="n"/>
     </row>
-    <row r="37">
-      <c r="A37" s="33" t="n">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="17" t="n"/>
-      <c r="C37" s="17" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="17" t="n"/>
+      <c r="B37" s="38" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="38" t="n"/>
       <c r="F37" s="4" t="n"/>
     </row>
-    <row r="38">
-      <c r="A38" s="33" t="n">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B38" s="17" t="n"/>
-      <c r="C38" s="17" t="n"/>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="17" t="n"/>
+      <c r="B38" s="38" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="38" t="n"/>
       <c r="F38" s="4" t="n"/>
     </row>
-    <row r="39">
-      <c r="A39" s="33" t="n">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="17" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="17" t="n"/>
+      <c r="B39" s="38" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="38" t="n"/>
       <c r="F39" s="4" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="33" t="n">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="17" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="17" t="n"/>
+      <c r="B40" s="38" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="38" t="n"/>
       <c r="F40" s="4" t="n"/>
     </row>
-    <row r="41">
-      <c r="A41" s="33" t="n">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="17" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="17" t="n"/>
+      <c r="B41" s="38" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="38" t="n"/>
       <c r="F41" s="4" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="33" t="n">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="17" t="n"/>
-      <c r="D42" s="30" t="n"/>
-      <c r="E42" s="17" t="n"/>
+      <c r="B42" s="38" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="38" t="n"/>
       <c r="F42" s="4" t="n"/>
     </row>
-    <row r="43">
-      <c r="A43" s="33" t="n">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="17" t="n"/>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="17" t="n"/>
+      <c r="B43" s="38" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="38" t="n"/>
       <c r="F43" s="4" t="n"/>
     </row>
     <row r="44">
@@ -1769,21 +1957,21 @@
       <c r="F46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="34" t="n"/>
+      <c r="A47" s="40" t="n"/>
       <c r="B47" s="4" t="n"/>
-      <c r="C47" s="34" t="n"/>
+      <c r="C47" s="40" t="n"/>
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+      <c r="A48" s="41" t="inlineStr">
         <is>
           <t>ELABORÓ</t>
         </is>
       </c>
       <c r="B48" s="4" t="n"/>
-      <c r="C48" s="35" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
         <is>
           <t>REVISÓ</t>
         </is>
@@ -1811,8 +1999,11 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E34:E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="D34:D43" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="FECHA NO VÁLIDA" error="Escribe una fecha válida, por ejemplo 15/03/2026." promptTitle="FECHA" prompt="Formato DD/MM/AAAA" type="date" errorStyle="warning" operator="greaterThan">
+      <formula1>36526</formula1>
+    </dataValidation>
+    <dataValidation sqref="E34:E43" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="OPCIÓN NO VÁLIDA" error="Elige una opción de la lista (puedes editarla en la hoja CATÁLOGOS)." promptTitle="SELECCIONA" prompt="Elige una opción de la lista desplegable." type="list">
       <formula1>"Pendiente,En proceso,Cumplido"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1849,7 +2040,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="36" t="inlineStr">
+      <c r="B1" s="42" t="inlineStr">
         <is>
           <t>AYUDA Y PREGUNTAS FRECUENTES</t>
         </is>
@@ -1860,7 +2051,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="43" t="inlineStr">
         <is>
           <t>MINUTA DE REUNIÓN</t>
         </is>
@@ -1897,12 +2088,12 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>¿Cuánto debe durar una minuta?</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="D6" s="45" t="inlineStr">
         <is>
           <t>Una o dos páginas; registra decisiones, no cada comentario.</t>
         </is>
@@ -1912,12 +2103,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>¿Debe firmarse?</t>
         </is>
       </c>
-      <c r="D7" s="39" t="inlineStr">
+      <c r="D7" s="45" t="inlineStr">
         <is>
           <t>Es recomendable en reuniones de comité, juntas con clientes o asuntos legales.</t>
         </is>
@@ -1927,12 +2118,12 @@
     <row r="8" ht="53" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>¿Por qué no puedo escribir en algunas celdas?</t>
         </is>
       </c>
-      <c r="D8" s="39" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
         </is>
@@ -1942,12 +2133,12 @@
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>¿Cómo agrego mi logotipo?</t>
         </is>
       </c>
-      <c r="D9" s="39" t="inlineStr">
+      <c r="D9" s="45" t="inlineStr">
         <is>
           <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
         </is>
@@ -1957,12 +2148,12 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
         </is>
@@ -1972,12 +2163,12 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>¿Con qué versiones de Excel funciona?</t>
         </is>
       </c>
-      <c r="D11" s="39" t="inlineStr">
+      <c r="D11" s="45" t="inlineStr">
         <is>
           <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
         </is>
@@ -1987,14 +2178,14 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>¿Por qué la letra se ve diferente?</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="inlineStr">
-        <is>
-          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>¿Puedo cambiar la letra?</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Arial, disponible en Windows, Mac y Google Sheets. Si necesitas otra, selecciona todo (Ctrl+E) y cambia la fuente; no afecta el funcionamiento.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -2002,12 +2193,12 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>¿Puedo usarlo en varias empresas o por varios años?</t>
         </is>
       </c>
-      <c r="D13" s="39" t="inlineStr">
+      <c r="D13" s="45" t="inlineStr">
         <is>
           <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
         </is>
@@ -2035,12 +2226,12 @@
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>ORDEN DEL DÍA</t>
         </is>
       </c>
-      <c r="D16" s="41" t="inlineStr">
+      <c r="D16" s="47" t="inlineStr">
         <is>
           <t>Temas a tratar.</t>
         </is>
@@ -2050,12 +2241,12 @@
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>ACUERDO</t>
         </is>
       </c>
-      <c r="D17" s="41" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr">
         <is>
           <t>Decisión tomada en la reunión.</t>
         </is>
@@ -2065,12 +2256,12 @@
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>COMPROMISO</t>
         </is>
       </c>
-      <c r="D18" s="41" t="inlineStr">
+      <c r="D18" s="47" t="inlineStr">
         <is>
           <t>Actividad asignada con responsable y fecha.</t>
         </is>
@@ -2097,12 +2288,12 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="48" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>Asistentes registrados</t>
         </is>
@@ -2112,12 +2303,12 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="48" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>Acuerdos redactados</t>
         </is>
@@ -2127,12 +2318,12 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="48" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>Compromisos con responsable y fecha</t>
         </is>
@@ -2142,12 +2333,12 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="48" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>Minuta enviada a todos</t>
         </is>
